--- a/01_Data/03_Test_Cases/IEEE 14/03_Escenarios/01 - wo Stress/caso_IEEE14_E1_24h.xlsx
+++ b/01_Data/03_Test_Cases/IEEE 14/03_Escenarios/01 - wo Stress/caso_IEEE14_E1_24h.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\03_Test_Cases\IEEE 14\03_Escenarios\01 - wo Stress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\2. Universidad Nacional de Colombia\2. Postgraduate\1_SEMESTER\TESIS DE MAESTRIA\2nd Search\04_TESIS_DANIEL\03_CODIGO_TRABAJO_DANIEL\BESS_FACTS_master\01_Data\03_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAC9476-B940-4342-B9AA-41357218CC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8246E9-4126-4B9E-AD6D-36B5A857049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,24 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={B724A91F-041A-4828-AFE4-51B44276F97E}</author>
+  </authors>
+  <commentList>
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{B724A91F-041A-4828-AFE4-51B44276F97E}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    acepta una solución dentro del 1% del óptimo </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={B6DC2CC3-29EA-4A10-A8D6-BBDEE50FBF22}</author>
   </authors>
   <commentList>
@@ -63,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="163">
   <si>
     <t>Plantilla de datos - Modelo TEP con BESS y FACTS</t>
   </si>
@@ -368,12 +386,6 @@
     <t>linea</t>
   </si>
   <si>
-    <t>dB_min</t>
-  </si>
-  <si>
-    <t>dB_max</t>
-  </si>
-  <si>
     <t>Demanda - Perfil horario de demanda por nodo</t>
   </si>
   <si>
@@ -534,6 +546,30 @@
   </si>
   <si>
     <t>CREG</t>
+  </si>
+  <si>
+    <t>habilitada</t>
+  </si>
+  <si>
+    <t>sigma_niveles</t>
+  </si>
+  <si>
+    <t>[USD/MVAr]</t>
+  </si>
+  <si>
+    <t>c_tcsc</t>
+  </si>
+  <si>
+    <t>theta_max_grados</t>
+  </si>
+  <si>
+    <t>solver</t>
+  </si>
+  <si>
+    <t>gurobi</t>
+  </si>
+  <si>
+    <t>0.15,0.30,0.45,0.60</t>
   </si>
 </sst>
 </file>
@@ -691,10 +727,12 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1005,6 +1043,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C10" dT="2026-08-10T19:38:57.45" personId="{18CA4A9A-668D-4DAC-B2F8-E20634DBE893}" id="{B724A91F-041A-4828-AFE4-51B44276F97E}">
+    <text xml:space="preserve">acepta una solución dentro del 1% del óptimo </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E4" dT="2026-08-01T22:40:11.33" personId="{18CA4A9A-668D-4DAC-B2F8-E20634DBE893}" id="{B6DC2CC3-29EA-4A10-A8D6-BBDEE50FBF22}">
     <text>Se realiza suposiciones para la rampa ya que no lo trae el modelo IEEE comparativo de MATPOWER. 
 1. Se puede fijar en Pmax para un despacho inmediato (solo para validacion de datos)
@@ -1112,7 +1158,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -1125,7 +1171,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -1138,46 +1184,28 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1195,23 +1223,23 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>41</v>
@@ -1223,22 +1251,22 @@
         <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2196,12 +2224,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2299,50 +2327,86 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B12" s="7">
         <v>15</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B13" s="7">
         <v>20</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" s="11">
         <v>1</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B15" s="11">
         <v>0.115</v>
       </c>
       <c r="C15" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="11">
+        <v>135000</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>156</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2386,10 +2450,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -2397,10 +2461,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="5">
         <v>21.7</v>
@@ -2408,10 +2472,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C8" s="5">
         <v>94.2</v>
@@ -2422,7 +2486,7 @@
         <v>41</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="5">
         <v>47.8</v>
@@ -2433,7 +2497,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" s="5">
         <v>7.6</v>
@@ -2444,7 +2508,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C11" s="5">
         <v>11.2</v>
@@ -2452,10 +2516,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C12" s="5">
         <v>0</v>
@@ -2463,10 +2527,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="5">
         <v>0</v>
@@ -2474,10 +2538,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" s="5">
         <v>29.5</v>
@@ -2485,10 +2549,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C15" s="5">
         <v>9</v>
@@ -2496,10 +2560,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C16" s="5">
         <v>3.5</v>
@@ -2507,10 +2571,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C17" s="5">
         <v>6.1</v>
@@ -2518,10 +2582,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C18" s="5">
         <v>13.5</v>
@@ -2529,10 +2593,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C19" s="5">
         <v>14.9</v>
@@ -2602,13 +2666,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D6" s="5">
         <v>1.9380000000000001E-2</v>
@@ -2616,16 +2680,16 @@
       <c r="E6" s="5">
         <v>5.917E-2</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="14">
         <v>155.60399999999998</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -2636,19 +2700,19 @@
       <c r="E7" s="5">
         <v>0.22303999999999999</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="14">
         <v>77.591999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D8" s="5">
         <v>4.6989999999999997E-2</v>
@@ -2656,16 +2720,16 @@
       <c r="E8" s="5">
         <v>0.19797000000000001</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="14">
         <v>66.707999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>41</v>
@@ -2676,16 +2740,16 @@
       <c r="E9" s="5">
         <v>0.17632</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="14">
         <v>58.704000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>42</v>
@@ -2696,16 +2760,16 @@
       <c r="E10" s="5">
         <v>0.17388000000000001</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="14">
         <v>44.735999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>41</v>
@@ -2716,13 +2780,13 @@
       <c r="E11" s="5">
         <v>0.17102999999999999</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="14">
         <v>13.452</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>41</v>
@@ -2736,19 +2800,19 @@
       <c r="E12" s="5">
         <v>4.2110000000000002E-2</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="14">
         <v>59.003999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D13" s="5">
         <v>0</v>
@@ -2756,19 +2820,19 @@
       <c r="E13" s="5">
         <v>0.20912</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="14">
         <v>27.42</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D14" s="5">
         <v>0</v>
@@ -2776,13 +2840,13 @@
       <c r="E14" s="5">
         <v>0.55618000000000001</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="14">
         <v>17.808</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>42</v>
@@ -2796,19 +2860,19 @@
       <c r="E15" s="5">
         <v>0.25202000000000002</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="14">
         <v>50.472000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D16" s="5">
         <v>9.4979999999999995E-2</v>
@@ -2816,19 +2880,19 @@
       <c r="E16" s="5">
         <v>0.19889999999999999</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="14">
         <v>7.3079999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D17" s="5">
         <v>0.12291000000000001</v>
@@ -2836,19 +2900,19 @@
       <c r="E17" s="5">
         <v>0.25580999999999998</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="14">
         <v>9.18</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="5">
         <v>6.615E-2</v>
@@ -2856,19 +2920,19 @@
       <c r="E18" s="5">
         <v>0.13027</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="14">
         <v>20.544</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D19" s="5">
         <v>0</v>
@@ -2876,19 +2940,19 @@
       <c r="E19" s="5">
         <v>0.17615</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="14">
         <v>10.188000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="D20" s="5">
         <v>0</v>
@@ -2896,19 +2960,19 @@
       <c r="E20" s="5">
         <v>0.11001</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="14">
         <v>37.607999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D21" s="5">
         <v>3.1809999999999998E-2</v>
@@ -2916,19 +2980,19 @@
       <c r="E21" s="5">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="14">
         <v>7.7880000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D22" s="5">
         <v>0.12711</v>
@@ -2936,19 +3000,19 @@
       <c r="E22" s="5">
         <v>0.27038000000000001</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="14">
         <v>12.239999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D23" s="5">
         <v>8.2049999999999998E-2</v>
@@ -2956,19 +3020,19 @@
       <c r="E23" s="5">
         <v>0.19206999999999999</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="14">
         <v>3.0359999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D24" s="5">
         <v>0.22092000000000001</v>
@@ -2976,19 +3040,19 @@
       <c r="E24" s="5">
         <v>0.19988</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="14">
         <v>1.776</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D25" s="5">
         <v>0.17093</v>
@@ -2996,7 +3060,7 @@
       <c r="E25" s="5">
         <v>0.34802</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="14">
         <v>5.8559999999999999</v>
       </c>
     </row>
@@ -3117,7 +3181,7 @@
         <v>64</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>65</v>
@@ -3169,10 +3233,10 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" s="5">
         <v>0</v>
@@ -3212,10 +3276,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="5">
         <v>0</v>
@@ -3255,10 +3319,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C8" s="5">
         <v>0</v>
@@ -3297,7 +3361,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>43</v>
@@ -3339,10 +3403,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C10" s="5">
         <v>0</v>
@@ -3509,7 +3573,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="16" customWidth="1"/>
@@ -3583,16 +3647,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
       </c>
-      <c r="C6" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D6" s="14">
-        <v>241000</v>
+      <c r="C6" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D6" s="15">
+        <v>6025</v>
       </c>
       <c r="E6" s="13">
         <f>SQRT(0.85)</f>
@@ -3614,16 +3678,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
       </c>
-      <c r="C7" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D7" s="14">
-        <v>241000</v>
+      <c r="C7" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D7" s="15">
+        <v>6025</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" ref="E7:F19" si="0">SQRT(0.85)</f>
@@ -3645,16 +3709,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5">
         <v>0</v>
       </c>
-      <c r="C8" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D8" s="14">
-        <v>241000</v>
+      <c r="C8" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D8" s="15">
+        <v>6025</v>
       </c>
       <c r="E8" s="13">
         <f t="shared" si="0"/>
@@ -3681,11 +3745,11 @@
       <c r="B9" s="5">
         <v>0</v>
       </c>
-      <c r="C9" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D9" s="14">
-        <v>241000</v>
+      <c r="C9" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D9" s="15">
+        <v>6025</v>
       </c>
       <c r="E9" s="13">
         <f t="shared" si="0"/>
@@ -3712,11 +3776,11 @@
       <c r="B10" s="5">
         <v>0</v>
       </c>
-      <c r="C10" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D10" s="14">
-        <v>241000</v>
+      <c r="C10" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D10" s="15">
+        <v>6025</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" si="0"/>
@@ -3743,11 +3807,11 @@
       <c r="B11" s="5">
         <v>0</v>
       </c>
-      <c r="C11" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D11" s="14">
-        <v>241000</v>
+      <c r="C11" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D11" s="15">
+        <v>6025</v>
       </c>
       <c r="E11" s="13">
         <f t="shared" si="0"/>
@@ -3769,16 +3833,16 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" s="5">
         <v>0</v>
       </c>
-      <c r="C12" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D12" s="14">
-        <v>241000</v>
+      <c r="C12" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D12" s="15">
+        <v>6025</v>
       </c>
       <c r="E12" s="13">
         <f t="shared" si="0"/>
@@ -3800,16 +3864,16 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B13" s="5">
         <v>0</v>
       </c>
-      <c r="C13" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D13" s="14">
-        <v>241000</v>
+      <c r="C13" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D13" s="15">
+        <v>6025</v>
       </c>
       <c r="E13" s="13">
         <f t="shared" si="0"/>
@@ -3831,16 +3895,16 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B14" s="5">
         <v>0</v>
       </c>
-      <c r="C14" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D14" s="14">
-        <v>241000</v>
+      <c r="C14" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D14" s="15">
+        <v>6025</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="0"/>
@@ -3862,16 +3926,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B15" s="5">
         <v>0</v>
       </c>
-      <c r="C15" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D15" s="14">
-        <v>241000</v>
+      <c r="C15" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D15" s="15">
+        <v>6025</v>
       </c>
       <c r="E15" s="13">
         <f t="shared" si="0"/>
@@ -3893,16 +3957,16 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B16" s="5">
         <v>0</v>
       </c>
-      <c r="C16" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D16" s="14">
-        <v>241000</v>
+      <c r="C16" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D16" s="15">
+        <v>6025</v>
       </c>
       <c r="E16" s="13">
         <f t="shared" si="0"/>
@@ -3924,16 +3988,16 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="C17" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D17" s="14">
-        <v>241000</v>
+      <c r="C17" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D17" s="15">
+        <v>6025</v>
       </c>
       <c r="E17" s="13">
         <f t="shared" si="0"/>
@@ -3955,16 +4019,16 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B18" s="5">
         <v>0</v>
       </c>
-      <c r="C18" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D18" s="14">
-        <v>241000</v>
+      <c r="C18" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D18" s="15">
+        <v>6025</v>
       </c>
       <c r="E18" s="13">
         <f t="shared" si="0"/>
@@ -3986,16 +4050,16 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
       </c>
-      <c r="C19" s="14">
-        <v>372000</v>
-      </c>
-      <c r="D19" s="14">
-        <v>241000</v>
+      <c r="C19" s="15">
+        <v>9300</v>
+      </c>
+      <c r="D19" s="15">
+        <v>6025</v>
       </c>
       <c r="E19" s="13">
         <f t="shared" si="0"/>
@@ -4014,9 +4078,6 @@
       <c r="I19" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C20" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
